--- a/GPS-Module-PCB/Project Outputs for GPS-Module-PCB/BOM/Bill of Materials-GPS-Module-New.xlsx
+++ b/GPS-Module-PCB/Project Outputs for GPS-Module-PCB/BOM/Bill of Materials-GPS-Module-New.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QRBOTS\PCB Projects\GPS_Mini_Only\GPS-Module-PCB\Project Outputs for GPS-Module-PCB\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E074D750-808E-4124-B1F4-743EA29038B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E07B5416-4642-4B7D-ABBF-E102484006DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{6C1844B9-B241-438D-8FED-053D90F7D1BA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D9CE99AE-DF83-4AA9-8C84-1AB14496D7AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-GPS-Module-Ne" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
     <t/>
   </si>
   <si>
-    <t>GEO, RTK, SAFE_B, TIME_P, TX_R</t>
+    <t>EXTINT, GEO, RTK, SAFE_B, TIME_P, TX_R</t>
   </si>
   <si>
     <t>USB4105-GF-A</t>
@@ -842,7 +842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6176964-AB48-4CBE-9339-E04C07951D22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A794D5-1AE2-44C3-8345-C7A938448125}">
   <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1024,7 +1024,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="1"/>
     </row>
@@ -1504,7 +1504,7 @@
       <c r="E33" s="1">
         <v>1</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="2" t="s">
         <v>132</v>
       </c>
     </row>

--- a/GPS-Module-PCB/Project Outputs for GPS-Module-PCB/BOM/Bill of Materials-GPS-Module-New.xlsx
+++ b/GPS-Module-PCB/Project Outputs for GPS-Module-PCB/BOM/Bill of Materials-GPS-Module-New.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QRBOTS\PCB Projects\GPS_Mini_Only\GPS-Module-PCB\Project Outputs for GPS-Module-PCB\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E07B5416-4642-4B7D-ABBF-E102484006DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC7A4368-A0D7-4F00-96FE-9BDC430C89C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D9CE99AE-DF83-4AA9-8C84-1AB14496D7AE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{336B5C3F-913B-4E83-A0AE-FA77530C72CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-GPS-Module-Ne" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="139">
   <si>
     <t>Comment</t>
   </si>
@@ -128,13 +128,22 @@
     <t>10nF</t>
   </si>
   <si>
-    <t>0402 10000 pF 16 V ±10% Tolerance X7R Multilayer Ceramic Chip Capacitor, Multilayer Ceramic Capacitors MLCC - SMD/SMT 25V 0.01uF X7R 0402 10%</t>
-  </si>
-  <si>
-    <t>C9, C10</t>
-  </si>
-  <si>
-    <t>GRM155R71C103KA01D, C0402C103K3REC7411</t>
+    <t>0402 10000 pF 16 V ±10% Tolerance X7R Multilayer Ceramic Chip Capacitor</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>GRM155R71C103KA01D</t>
+  </si>
+  <si>
+    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 25V 0.01uF X7R 0402 10%</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C0402C103K3REC7411</t>
   </si>
   <si>
     <t>PESD0402-140</t>
@@ -842,8 +851,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A794D5-1AE2-44C3-8345-C7A938448125}">
-  <dimension ref="A1:F33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7D370E5-8EA4-4611-AF8B-9D9064B1C5B9}">
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="19" customWidth="1"/>
@@ -984,7 +993,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>31</v>
@@ -992,41 +1001,43 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E9" s="1">
-        <v>6</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -1039,293 +1050,291 @@
         <v>41</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="1">
-        <v>2</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="1">
-        <v>3</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="1">
-        <v>2</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1339,7 +1348,7 @@
         <v>102</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -1350,162 +1359,182 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>132</v>
+      <c r="B34" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
